--- a/crew_102.xlsx
+++ b/crew_102.xlsx
@@ -459,7 +459,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-16 13:01:00</t>
+          <t>Timestamp: 2026-07-16 13:31:00</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>661268</v>
+        <v>663396</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>3149</v>
+        <v>3159</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>334108</v>
+        <v>336215</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>478837</v>
+        <v>480934</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2283</v>
+        <v>2293</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>302990</v>
+        <v>305102</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1443</v>
+        <v>1453</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>427836</v>
+        <v>444804</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2031</v>
+        <v>2112</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>482854</v>
+        <v>484776</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2300</v>
+        <v>2309</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>281644</v>
+        <v>283780</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1340</v>
+        <v>1350</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>278603</v>
+        <v>280703</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1327</v>
+        <v>1337</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>490554</v>
+        <v>496689</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2334</v>
+        <v>2363</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>395952</v>
+        <v>398041</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1884</v>
+        <v>1894</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>460326</v>
+        <v>476530</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2030</v>
+        <v>2107</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>398385</v>
+        <v>402137</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1897</v>
+        <v>1915</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>375091</v>
+        <v>377179</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>476107</v>
+        <v>491853</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>2103</v>
+        <v>2178</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>493007</v>
+        <v>509328</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>2174</v>
+        <v>2252</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>212916</v>
+        <v>215043</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>473536</v>
+        <v>486139</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2093</v>
+        <v>2153</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>312365</v>
+        <v>314456</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>559700</v>
+        <v>561829</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>2663</v>
+        <v>2673</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>315619</v>
+        <v>317729</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1503</v>
+        <v>1513</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>275757</v>
+        <v>277880</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1244</v>
+        <v>1254</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>349330</v>
+        <v>351451</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1665</v>
+        <v>1675</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>281281</v>
+        <v>281699</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>328488</v>
+        <v>330789</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>397075</v>
+        <v>403334</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1730</v>
+        <v>1760</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>175902</v>
+        <v>183748</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>838</v>
+        <v>875</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>296068</v>
+        <v>298194</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1412</v>
+        <v>1422</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>213727</v>
+        <v>215847</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1018</v>
+        <v>1028</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>279631</v>
+        <v>281694</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1329</v>
+        <v>1339</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>320074</v>
+        <v>322208</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1523</v>
+        <v>1533</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>447652</v>
+        <v>449738</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>2132</v>
+        <v>2142</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>242652</v>
+        <v>244762</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>366923</v>
+        <v>369011</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1749</v>
+        <v>1759</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>276131</v>
+        <v>278638</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1316</v>
+        <v>1328</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>321214</v>
+        <v>323305</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1465</v>
+        <v>1475</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>

--- a/crew_102.xlsx
+++ b/crew_102.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="2026-07-16" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026-07-17" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,7 +453,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Blood Brothers (102)</t>
+          <t>Crew: Blood Brothers (102) | S28 P1</t>
         </is>
       </c>
     </row>
@@ -1403,6 +1404,992 @@
       </c>
       <c r="D43" s="5" t="n">
         <v>1475</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Blood Brothers (102) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-17 13:54:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>748437</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+85041</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3563</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>391577</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+55362</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>554189</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+73255</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2642</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>488807</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+146949</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2205</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>418271</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+113169</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>531666</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+86862</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2526</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>568086</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+83310</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2705</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>385937</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+102157</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1837</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>383480</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+102777</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1826</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>271461</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+92961</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1294</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>635089</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+138400</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3022</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>496666</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+98625</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2364</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>564307</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+87777</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2525</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Pencilgon</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>533754</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+131617</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2542</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>412098</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+96123</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1960</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>419960</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+42781</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>552895</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+61042</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2469</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>568551</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+71678</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>2663</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>569878</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+60550</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>2540</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>301113</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+86070</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1434</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>565295</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+79156</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2530</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>417227</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+102771</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1987</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>606289</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+44460</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>2885</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>447829</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+130100</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2133</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>332672</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+54792</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1514</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>~Pria_SoL0~</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>487885</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+136434</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2325</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>397397</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+115698</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1894</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>388104</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+57315</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1673</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>601479</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+198145</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>2704</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>258100</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1229</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Armando</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>408877</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+110683</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>1949</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>561879</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+82807</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>300753</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+84906</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1433</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>374576</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+92882</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1781</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>424198</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+101990</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>518039</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+68301</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>2468</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Breaker MAX</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>358784</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+114022</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>1709</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>482531</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+113520</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>2299</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>375874</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+97236</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>1791</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>374221</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+50916</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1719</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>

--- a/crew_102.xlsx
+++ b/crew_102.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="2026-07-16" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2026-07-17" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-07-18" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2404,4 +2405,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Blood Brothers (102) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-18 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>872545</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+124108</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4155</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>+996</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>420631</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+29054</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1938</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>+402</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>660255</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+106066</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3147</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+854</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>595746</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+106939</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2587</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+961</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>532626</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+114355</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2536</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+1083</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>670362</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+138696</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3187</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>+1075</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>657465</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+89379</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3130</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>+821</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>452218</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+66281</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2152</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>+802</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>487068</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+103588</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2320</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>+983</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>363864</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+92403</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1735</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>+884</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>754709</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+119620</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3592</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>+1229</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>782280</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+285614</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3726</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>+1832</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>691353</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+127046</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3131</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>+1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Pencilgon</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>642316</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+108562</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3059</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>+1144</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>515464</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+103366</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2452</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>+948</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>485605</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+65645</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2313</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>+516</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>666005</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+113110</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3007</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>+829</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>649300</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+80749</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3048</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>+727</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>684459</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+114581</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3086</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>+834</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>418946</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+117833</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>+969</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>710550</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+145255</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3223</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>+1070</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>552150</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+134923</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>+1133</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>688737</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+82448</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3278</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>+605</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>556449</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+108620</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>+1138</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>361761</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+29089</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>+399</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>~Pria_SoL0~</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>601854</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+113969</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2868</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>+1193</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>499095</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+101698</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2378</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>+1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>474323</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+86219</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2084</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>+685</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>683664</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+82185</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3096</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>+1336</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>336157</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+78057</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Armando</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>518647</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+109770</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2472</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>+1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>630315</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+68436</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2957</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>+722</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>411655</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+110902</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1961</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>+933</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>468277</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+93701</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2227</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>+888</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>504328</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+80130</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>+867</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>595633</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+77594</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>2838</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>+696</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Breaker MAX</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>464969</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+106185</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>2214</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>+1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>600649</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+118118</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>2861</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>+1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>471583</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+95709</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2246</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>+918</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>396602</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+22381</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1826</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>+351</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_102.xlsx
+++ b/crew_102.xlsx
@@ -10,6 +10,7 @@
     <sheet name="2026-07-16" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2026-07-17" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-07-18" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-07-19" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3391,4 +3392,658 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Blood Brothers (102) | S28 P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-19 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>965241</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+92696</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>420631</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>768088</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+107833</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>622507</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+26761</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>582781</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+50155</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>713131</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+42769</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>748427</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+90962</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>520082</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+67864</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>600678</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+113610</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>433475</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+69611</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>847577</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+92868</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>782280</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>734131</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+42778</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Pencilgon</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>758160</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+115844</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>595038</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+79574</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>576220</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+90615</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>711502</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+45497</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>649300</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>727247</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+42788</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>510701</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+91755</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>753410</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+42860</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>622614</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+70464</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>778955</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+90218</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>642025</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+85576</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>361761</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>~Pria_SoL0~</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>651992</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+50138</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>545590</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+46495</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>519668</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+45345</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>796528</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+112864</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>385722</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+49565</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Armando</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>568751</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+50104</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>630315</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>504470</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+92815</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>552584</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+84307</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>533002</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+28674</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>687418</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+91785</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Breaker MAX</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>568981</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+104012</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>686501</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+85852</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>556808</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+85225</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>396602</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_102.xlsx
+++ b/crew_102.xlsx
@@ -11,6 +11,7 @@
     <sheet name="2026-07-17" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-07-18" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2026-07-19" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-07-20" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4046,4 +4047,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Blood Brothers (102) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-20 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>965241</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4597</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>+442</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>420631</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1938</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>768088</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3662</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+515</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>631698</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+9191</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2682</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+95</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>582781</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2775</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+239</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>713131</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3391</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>+204</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>748427</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3563</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>+433</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>520082</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2474</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>+322</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>665549</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+64871</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2861</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>+541</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>433591</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+116</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2066</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>+331</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>847759</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+182</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4034</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>+442</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>782280</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3726</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>734131</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3335</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>+204</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Pencilgon</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>784959</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+26799</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3611</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>+552</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>622605</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+27567</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2831</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>+379</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>598601</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+22381</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2744</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>+431</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>711502</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3223</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>+216</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>649300</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3048</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>727247</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>+204</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>510701</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2431</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>+437</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>753410</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3427</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>+204</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>622614</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2966</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>+336</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>837427</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+58472</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3709</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>+431</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>642025</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3059</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>+408</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>361761</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>~Pria_SoL0~</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>651992</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3107</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>+239</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>545590</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>+222</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>519668</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>+216</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>796528</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3634</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>+538</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>400212</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+14490</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>+236</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Armando</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>568751</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2710</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>+238</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>630315</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2957</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>504470</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>2404</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>+443</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>552584</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2628</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>+401</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>622036</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+89034</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>2537</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>+137</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>752457</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+65039</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3275</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>+437</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Breaker MAX</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>577278</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+8297</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>2709</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>+495</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>686501</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3270</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>+409</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>642646</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+85838</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2652</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>+406</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>396602</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1826</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_102.xlsx
+++ b/crew_102.xlsx
@@ -12,6 +12,7 @@
     <sheet name="2026-07-18" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2026-07-19" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-07-20" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-07-21" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5033,4 +5034,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Blood Brothers (102) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-21 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>965241</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4597</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>+4597</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>420631</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1938</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>+1938</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>768088</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3662</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+3662</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>652656</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+20958</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2682</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+2682</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>582781</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2775</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+2775</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>713131</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3391</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>+3391</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>748427</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3563</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>+3563</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>769388</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+103839</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2861</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>+2861</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>433591</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2066</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>+2066</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>847759</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4034</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>+4034</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>782280</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3726</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>+3726</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>734131</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3335</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>+3335</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Pencilgon</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>819289</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+34330</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3611</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>+3611</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>650962</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+28357</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2831</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>+2831</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>611654</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+13053</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2744</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>+2744</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>711502</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3223</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>+3223</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>649300</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3048</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>+3048</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>727247</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>+3290</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>515207</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+4506</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2431</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>+2431</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>753410</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3427</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>+3427</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>622614</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2966</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>+2966</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>915230</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+77803</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3709</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>+3709</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>642025</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3059</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>+3059</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>361761</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>+1653</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>~Pria_SoL0~</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>651992</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3107</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>+3107</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>545590</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>+2600</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>519855</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+187</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>+2300</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>796528</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3634</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>+3634</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>412138</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+11926</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>+1836</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Armando</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>568751</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2710</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>+2710</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>630315</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2957</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>+2957</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>504470</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>2404</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>+2404</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>567882</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+15298</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2628</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>+2628</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>714942</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+92906</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>2537</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>+2537</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>765773</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+13316</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3275</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>+3275</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Breaker MAX</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>613054</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+35776</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>2709</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>+2709</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>686501</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3270</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>+3270</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>694058</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+51412</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2652</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>+2652</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>396602</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1826</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>+1826</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_102.xlsx
+++ b/crew_102.xlsx
@@ -13,6 +13,7 @@
     <sheet name="2026-07-19" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-07-20" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-07-21" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-07-22" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6020,4 +6021,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Blood Brothers (102) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-22 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>965241</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4597</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>420631</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1938</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>768088</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3662</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>652656</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2682</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>582781</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2775</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>713131</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3391</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>748427</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3563</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>864471</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+95083</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2861</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>433591</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2066</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>847759</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4034</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>782280</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3726</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>734131</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3335</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Pencilgon</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>822937</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+3648</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3611</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>689634</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+38672</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2831</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>649323</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+37669</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2744</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>711502</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3223</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>658040</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+8740</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3048</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>727247</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>520949</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+5742</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2431</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>753410</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3427</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>622614</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2966</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>954115</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+38885</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3709</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>642025</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3059</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>361761</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>~Pria_SoL0~</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>651992</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3107</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>545590</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>520044</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+189</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>796528</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3634</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>412138</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Armando</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>568751</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2710</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>637634</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+7319</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2957</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>504470</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>2404</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>582245</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+14363</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2628</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>758613</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+43671</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>2537</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>770204</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+4431</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3275</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Breaker MAX</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>716882</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+103828</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>2709</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>686501</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3270</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>750218</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+56160</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2652</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>396602</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1826</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_102.xlsx
+++ b/crew_102.xlsx
@@ -14,6 +14,7 @@
     <sheet name="2026-07-20" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-07-21" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-07-22" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026-07-23" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7007,4 +7008,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Blood Brothers (102) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-23 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>965241</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4597</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>420631</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1938</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>768088</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3662</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>652656</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2682</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>582781</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2775</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>734976</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+21845</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3391</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>748427</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3563</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>920786</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+56315</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2861</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>433591</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2066</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2388</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+2388</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>847759</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4034</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>782280</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3726</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>755921</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+21790</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3335</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Pencilgon</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>822937</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3611</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>697201</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+7567</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2831</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>649323</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2744</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>733354</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+21852</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3223</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>663940</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+5900</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3048</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>748952</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+21705</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>532230</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+11281</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2431</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>775216</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+21806</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3427</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>622614</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2966</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>958583</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+4468</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3709</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>642025</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3059</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>361761</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>~Pria_SoL0~</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>651992</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3107</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>545590</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>541769</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+21725</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>796528</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3634</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>412678</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Armando</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>568751</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2710</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>645639</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+8005</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2957</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>504470</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>2404</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>582245</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2628</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>763077</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+4464</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>2537</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>820061</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+49857</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3275</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Breaker MAX</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>820553</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+103671</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>2709</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>686501</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3270</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>753825</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+3607</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2652</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>396602</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1826</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_102.xlsx
+++ b/crew_102.xlsx
@@ -15,6 +15,7 @@
     <sheet name="2026-07-21" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-07-22" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2026-07-23" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026-07-24" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7994,4 +7995,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Blood Brothers (102) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-24 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>965241</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4597</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>420631</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1938</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>14517</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>768088</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3662</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>652656</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2682</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>582781</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2775</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>801892</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+66916</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3391</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>748609</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+182</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3563</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>987830</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+67044</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2861</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>433591</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2066</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2388</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>847759</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4034</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>782627</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+347</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3726</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>823384</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+67463</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3335</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Pencilgon</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>841317</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+18380</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3611</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>704591</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+7390</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2831</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>670902</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+21579</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2744</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>800176</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+66822</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3223</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>673111</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+9171</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3048</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>772752</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+23800</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>534389</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+2159</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2431</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>842336</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+67120</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3427</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>622614</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>2966</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1006154</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+47571</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3709</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>642025</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3059</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>361761</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>~Pria_SoL0~</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>651992</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3107</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>545590</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>621389</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+79620</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>796528</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3634</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>418466</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+5788</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Armando</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>568751</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2710</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>651447</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+5808</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>2957</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>582245</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2628</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>867165</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+104088</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>2537</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>833496</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+13435</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3275</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Breaker MAX</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>915704</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+95151</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>2709</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>686501</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3270</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>788414</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+34589</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2652</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>396602</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1826</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_102.xlsx
+++ b/crew_102.xlsx
@@ -16,6 +16,7 @@
     <sheet name="2026-07-22" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2026-07-23" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="2026-07-24" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2026-07-25" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1427,6 +1428,992 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Blood Brothers (102) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-25 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>965241</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4597</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>420631</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1938</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>66388</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+51871</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>768088</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3662</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>662051</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+9395</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2682</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>582781</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2775</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>880000</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+78108</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3391</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>761219</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+12610</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3563</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1020645</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+32815</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2861</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>433591</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2066</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2388</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>847759</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4034</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>790906</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+8279</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3726</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>903263</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+79879</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3335</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Pencilgon</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>872833</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+31516</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3611</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>713856</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+9265</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2831</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>670902</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2744</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>879893</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+79717</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3223</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>692123</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+19012</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3048</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>833472</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+60720</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>534389</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2431</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>920029</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+77693</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3427</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>622614</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>2966</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1006154</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3709</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>642025</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3059</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>361761</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>~Pria_SoL0~</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>651992</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3107</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>545590</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>699210</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+77821</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>796528</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3634</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>418466</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Armando</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>568751</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2710</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>659431</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+7984</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>2957</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>582245</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2628</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>962016</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+94851</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>2537</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>876303</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+42807</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3275</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Breaker MAX</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>915704</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>2709</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>686501</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3270</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>832877</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+44463</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2652</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>396602</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1826</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/crew_102.xlsx
+++ b/crew_102.xlsx
@@ -1447,7 +1447,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Blood Brothers (102) | S28 P1</t>
+          <t>Crew: Blood Brothers (102) | S28 P2</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Blood Brothers (102) | S28 P2</t>
+          <t>Crew: Blood Brothers (102) | S28 P1</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Blood Brothers (102) | S28 P1</t>
+          <t>Crew: Blood Brothers (102) | S28 P2</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Blood Brothers (102) | S28 P1</t>
+          <t>Crew: Blood Brothers (102) | S28 P2</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Blood Brothers (102) | S28 P1</t>
+          <t>Crew: Blood Brothers (102) | S28 P2</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Blood Brothers (102) | S28 P1</t>
+          <t>Crew: Blood Brothers (102) | S28 P2</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Blood Brothers (102) | S28 P1</t>
+          <t>Crew: Blood Brothers (102) | S28 P2</t>
         </is>
       </c>
     </row>
